--- a/plantillas/02_Proyectos.xlsx
+++ b/plantillas/02_Proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\municipio-inversiones\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F508A965-E330-46AE-B643-E4436FF3714E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32387828-0A89-41E2-8041-9367C170B360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13694,7 +13694,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF7C3AED"/>
   </sheetPr>
   <dimension ref="A1:L76"/>
@@ -13749,7 +13749,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22">
         <v>202500000047571</v>
       </c>
@@ -13787,7 +13787,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21">
         <v>202500000047555</v>
       </c>
@@ -13825,7 +13825,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22">
         <v>202500000047627</v>
       </c>
@@ -13863,7 +13863,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21">
         <v>202500000048502</v>
       </c>
@@ -13901,7 +13901,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22">
         <v>202500000047627</v>
       </c>
@@ -13939,7 +13939,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
         <v>202500000048222</v>
       </c>
@@ -13977,7 +13977,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22">
         <v>202500000048210</v>
       </c>
@@ -14015,7 +14015,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21">
         <v>202500000047420</v>
       </c>
@@ -14053,7 +14053,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22">
         <v>202500000047420</v>
       </c>
@@ -14091,7 +14091,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21">
         <v>202500000048180</v>
       </c>
@@ -14129,7 +14129,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="22">
         <v>202500000047627</v>
       </c>
@@ -14167,7 +14167,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21">
         <v>202500000047762</v>
       </c>
@@ -14205,7 +14205,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="22">
         <v>202500000049057</v>
       </c>
@@ -14243,7 +14243,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="21">
         <v>202500000049057</v>
       </c>
@@ -14281,7 +14281,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="22">
         <v>202500000048251</v>
       </c>
@@ -14319,7 +14319,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="21">
         <v>202500000048881</v>
       </c>
@@ -14357,7 +14357,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="22">
         <v>202500000049057</v>
       </c>
@@ -14395,7 +14395,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="21">
         <v>202500000049049</v>
       </c>
@@ -14433,7 +14433,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="22">
         <v>202500000047420</v>
       </c>
@@ -14471,7 +14471,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="21">
         <v>202500000049057</v>
       </c>
@@ -14509,7 +14509,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="22">
         <v>202500000049057</v>
       </c>
@@ -14547,7 +14547,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="21">
         <v>202500000047420</v>
       </c>
@@ -14585,7 +14585,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="22">
         <v>202500000047627</v>
       </c>
@@ -14623,7 +14623,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="21">
         <v>202500000048210</v>
       </c>
@@ -14661,7 +14661,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="22">
         <v>202500000048180</v>
       </c>
@@ -14699,7 +14699,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="21">
         <v>202500000047420</v>
       </c>
@@ -14813,7 +14813,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22">
         <v>202500000047506</v>
       </c>
@@ -14851,7 +14851,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="21">
         <v>202500000047498</v>
       </c>
@@ -14889,7 +14889,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="22">
         <v>202500000048210</v>
       </c>
@@ -14927,7 +14927,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="21">
         <v>202500000047762</v>
       </c>
@@ -15041,7 +15041,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="22">
         <v>202500000047953</v>
       </c>
@@ -15117,7 +15117,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="22">
         <v>202500000048257</v>
       </c>
@@ -15193,7 +15193,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22">
         <v>202500000048206</v>
       </c>
@@ -15269,7 +15269,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22">
         <v>202500000047420</v>
       </c>
@@ -15307,7 +15307,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="21">
         <v>202500000047420</v>
       </c>
@@ -15345,7 +15345,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="22">
         <v>202500000049057</v>
       </c>
@@ -15383,7 +15383,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21">
         <v>202500000049043</v>
       </c>
@@ -15421,7 +15421,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="22">
         <v>202500000049049</v>
       </c>
@@ -15459,7 +15459,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21">
         <v>202500000047423</v>
       </c>
@@ -15497,7 +15497,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="22">
         <v>202500000048502</v>
       </c>
@@ -15573,7 +15573,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="22">
         <v>202500000047420</v>
       </c>
@@ -15611,7 +15611,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="21">
         <v>202500000047807</v>
       </c>
@@ -15649,7 +15649,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="22">
         <v>202500000048309</v>
       </c>
@@ -15687,7 +15687,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21">
         <v>202500000049057</v>
       </c>
@@ -15725,7 +15725,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="22">
         <v>202500000047652</v>
       </c>
@@ -15763,7 +15763,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="21">
         <v>202500000047404</v>
       </c>
@@ -15801,7 +15801,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="22">
         <v>202500000047652</v>
       </c>
@@ -15839,7 +15839,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21">
         <v>202500000049057</v>
       </c>
@@ -15877,7 +15877,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="22">
         <v>202500000049049</v>
       </c>
@@ -15915,7 +15915,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21">
         <v>202500000047538</v>
       </c>
@@ -15953,7 +15953,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="22">
         <v>202500000049057</v>
       </c>
@@ -15991,7 +15991,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21">
         <v>202500000048004</v>
       </c>
@@ -16029,7 +16029,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="22">
         <v>202600000006597</v>
       </c>
@@ -16067,7 +16067,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="21">
         <v>202500000048502</v>
       </c>
@@ -16105,7 +16105,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="22">
         <v>202500000047953</v>
       </c>
@@ -16143,7 +16143,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="21">
         <v>202500000047627</v>
       </c>
@@ -16181,7 +16181,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="22">
         <v>202500000047420</v>
       </c>
@@ -16219,7 +16219,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="21">
         <v>202500000047627</v>
       </c>
@@ -16257,7 +16257,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="22">
         <v>202600000006625</v>
       </c>
@@ -16295,7 +16295,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="21">
         <v>202500000047425</v>
       </c>
@@ -16333,7 +16333,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="22">
         <v>202500000047878</v>
       </c>
@@ -16371,7 +16371,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="21">
         <v>202500000048502</v>
       </c>
@@ -16447,7 +16447,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="21">
         <v>202500000048257</v>
       </c>
@@ -16516,13 +16516,7 @@
       <c r="L76" s="35"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L73" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="202500000047838"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L73" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A76:L76"/>
   </mergeCells>
